--- a/static/spark-cv/data/pubs.xlsx
+++ b/static/spark-cv/data/pubs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\spark\Documents\spark-webs\spark-web\public\spark-cv\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seonggpa\Documents\spark-web\spark-hydro.github.io\static\spark-cv\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1769D006-FA25-4FB4-882C-58664DF273E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB18976-716A-48C3-BF6D-F2353FCA14B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
+    <workbookView xWindow="19080" yWindow="3980" windowWidth="32150" windowHeight="15370" xr2:uid="{9662CE4C-DEF8-8749-ABE3-ABD9C0AA9720}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="419">
   <si>
     <t>authors</t>
   </si>
@@ -1213,6 +1213,84 @@
   </si>
   <si>
     <t>Jeju, South Korea</t>
+  </si>
+  <si>
+    <t>Sorando, R., Park, S., Jeong, J., Sanchis-Ibor, C. and Comin, F.A.</t>
+  </si>
+  <si>
+    <t>Simulating mediterranean rice paddies' water balance under climate change scenarios</t>
+  </si>
+  <si>
+    <t>Agricultural Water Management</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.agwat.2026.110313</t>
+  </si>
+  <si>
+    <t>10.1016/j.agwat.2026.110313</t>
+  </si>
+  <si>
+    <t>Integrated Random Forest and APEX-MODFLOW model for predicting and mapping river salinity in the Animas Watershed, Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Han, H., Park, S., Bazrkar, M.H., Abitew, T.A., Hong, Y. and Jeong, J.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.ejrh.2026.103302</t>
+  </si>
+  <si>
+    <t>10.1016/j.ejrh.2026.103302</t>
+  </si>
+  <si>
+    <t>Octobor, 2025</t>
+  </si>
+  <si>
+    <t>Park, S., Collins, S., Walker, S., Bernard, E., Bailey, R., Bawa, A., and Arnold, J.</t>
+  </si>
+  <si>
+    <t>Fort Collins, Colorado, US</t>
+  </si>
+  <si>
+    <t>Assessing Hydrological Impacts of Purified Produced Water Reuse in the Pecos River Basin Using SWAT+ gwflow</t>
+  </si>
+  <si>
+    <t>June, 2026</t>
+  </si>
+  <si>
+    <t>Park, S., Bawa, A., Collins, and S., Walker, S.</t>
+  </si>
+  <si>
+    <t>2026 UCOWR/NIWR Annual Water Resources Conference</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas, US</t>
+  </si>
+  <si>
+    <t>TxPWC 2026 Annual Members Meeting</t>
+  </si>
+  <si>
+    <t>Midland, Texas, US</t>
+  </si>
+  <si>
+    <t>Evaluating Hydrological Impacts of Purified Produced Water Reuse in the Pecos River Basin with SWAT+ gwflow</t>
+  </si>
+  <si>
+    <t>Park, S., Serrano, D., Collins, S., Walker, S., Bernard, E., Bailey, R., Bawa, A., and Arnold, J.</t>
+  </si>
+  <si>
+    <t>2026 International SWAT Conference</t>
+  </si>
+  <si>
+    <t>Thessaloniki, Greece</t>
+  </si>
+  <si>
+    <t>SURFACE DISCHARGE: Evaluating Hydrological Impacts of Produced Water Reuse</t>
+  </si>
+  <si>
+    <t>August,2026</t>
+  </si>
+  <si>
+    <t>Assessing Salinity Sources and Baseflow Constraints in the Pecos River Basin using SWAT+ gwflow</t>
   </si>
 </sst>
 </file>
@@ -1740,31 +1818,31 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF752879-4E41-3C4A-A16F-F1C105CAD07B}">
-  <dimension ref="A1:Y102"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6"/>
+  <dimension ref="A1:Y111"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="14.19921875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" style="2" customWidth="1"/>
     <col min="2" max="2" width="11" style="2"/>
-    <col min="3" max="3" width="30.296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="11" style="2"/>
     <col min="5" max="5" width="35.5" style="2" customWidth="1"/>
-    <col min="6" max="6" width="14.69921875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="7.796875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.796875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="7.83203125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="11" style="2"/>
-    <col min="11" max="11" width="35.19921875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.19921875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="35.1640625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.1640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="26" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9.69921875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" style="2" customWidth="1"/>
     <col min="15" max="15" width="11" style="2"/>
-    <col min="16" max="16" width="14.296875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" style="2" customWidth="1"/>
     <col min="17" max="17" width="11" style="2"/>
-    <col min="18" max="18" width="15.796875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="11.296875" style="2" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="11.33203125" style="2" customWidth="1"/>
     <col min="20" max="16384" width="11" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="31.2">
+    <row r="1" spans="1:25" ht="31">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
@@ -1841,38 +1919,18 @@
         <v>361</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="62.4">
-      <c r="A2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" s="1">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="G2" s="1">
-        <v>659</v>
-      </c>
+    <row r="2" spans="1:25">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-      <c r="I2" s="1">
-        <v>133288</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>386</v>
-      </c>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -1885,37 +1943,37 @@
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
     </row>
-    <row r="3" spans="1:25" ht="78">
+    <row r="3" spans="1:25" ht="46.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="D3" s="1">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>367</v>
+        <v>395</v>
       </c>
       <c r="G3" s="1">
-        <v>15</v>
+        <v>328</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1">
-        <v>1505</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>368</v>
+        <v>110313</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1929,37 +1987,37 @@
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
     </row>
-    <row r="4" spans="1:25" ht="46.8">
+    <row r="4" spans="1:25" ht="62">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>365</v>
+        <v>399</v>
       </c>
       <c r="D4" s="1">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c r="G4" s="1">
-        <v>952</v>
+        <v>64</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1">
-        <v>175914</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>364</v>
+        <v>103302</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>400</v>
       </c>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1973,37 +2031,37 @@
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
     </row>
-    <row r="5" spans="1:25" ht="46.8">
+    <row r="5" spans="1:25" ht="62">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>349</v>
+        <v>384</v>
       </c>
       <c r="D5" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>348</v>
+        <v>272</v>
       </c>
       <c r="G5" s="1">
-        <v>261</v>
+        <v>659</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1">
-        <v>104289</v>
+        <v>133288</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>352</v>
+        <v>385</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>351</v>
+        <v>386</v>
       </c>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
@@ -2017,37 +2075,37 @@
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
     </row>
-    <row r="6" spans="1:25" ht="46.8">
+    <row r="6" spans="1:25" ht="77.5">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D6" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>129</v>
+        <v>367</v>
       </c>
       <c r="G6" s="1">
-        <v>169</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1">
-        <v>105832</v>
+        <v>1505</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -2061,37 +2119,37 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" spans="1:25" ht="46.8">
+    <row r="7" spans="1:25" ht="46.5">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="D7" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>347</v>
+        <v>140</v>
       </c>
       <c r="G7" s="1">
-        <v>27</v>
-      </c>
-      <c r="H7" s="1">
-        <v>7</v>
-      </c>
-      <c r="I7" s="1"/>
+        <v>952</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1">
+        <v>175914</v>
+      </c>
       <c r="J7" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>344</v>
+        <v>363</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>364</v>
       </c>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
@@ -2105,37 +2163,37 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" spans="1:25" ht="46.8">
+    <row r="8" spans="1:25" ht="46.5">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="D8" s="1">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>181</v>
+        <v>348</v>
       </c>
       <c r="G8" s="1">
-        <v>165</v>
+        <v>261</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1">
-        <v>105723</v>
+        <v>104289</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
@@ -2149,37 +2207,37 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" spans="1:25" ht="62.4">
+    <row r="9" spans="1:25" ht="46.5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>302</v>
+        <v>356</v>
       </c>
       <c r="D9" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>301</v>
+        <v>353</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>326</v>
+        <v>129</v>
       </c>
       <c r="G9" s="1">
-        <v>81</v>
+        <v>169</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1">
-        <v>531</v>
+        <v>105832</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>330</v>
+        <v>355</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
@@ -2193,35 +2251,37 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
     </row>
-    <row r="10" spans="1:25" ht="62.4">
+    <row r="10" spans="1:25" ht="46.5">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B10" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="D10" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>273</v>
+        <v>347</v>
       </c>
       <c r="G10" s="1">
-        <v>146</v>
-      </c>
-      <c r="H10" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="H10" s="1">
+        <v>7</v>
+      </c>
       <c r="I10" s="1"/>
       <c r="J10" s="1" t="s">
-        <v>319</v>
+        <v>345</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>318</v>
+        <v>344</v>
       </c>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
@@ -2235,35 +2295,37 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
     </row>
-    <row r="11" spans="1:25" ht="46.8">
+    <row r="11" spans="1:25" ht="46.5">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="D11" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>272</v>
+        <v>181</v>
       </c>
       <c r="G11" s="1">
-        <v>610</v>
+        <v>165</v>
       </c>
       <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>105723</v>
+      </c>
       <c r="J11" s="1" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
@@ -2277,37 +2339,37 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
     </row>
-    <row r="12" spans="1:25" ht="62.4">
+    <row r="12" spans="1:25" ht="62">
       <c r="A12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="D12" s="1">
         <v>2022</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>272</v>
+        <v>326</v>
       </c>
       <c r="G12" s="1">
-        <v>606</v>
-      </c>
-      <c r="H12" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="H12" s="1"/>
       <c r="I12" s="1">
-        <v>127449</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>279</v>
+        <v>531</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
@@ -2321,36 +2383,35 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" spans="1:25" ht="62.4">
+    <row r="13" spans="1:25" ht="62">
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>132</v>
+        <v>316</v>
       </c>
       <c r="D13" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>128</v>
+        <v>317</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>129</v>
+        <v>273</v>
       </c>
       <c r="G13" s="1">
-        <v>134</v>
-      </c>
-      <c r="I13" s="17">
-        <v>105093</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
       <c r="J13" s="1" t="s">
-        <v>130</v>
+        <v>319</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>131</v>
+        <v>318</v>
       </c>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
@@ -2360,38 +2421,39 @@
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
-    </row>
-    <row r="14" spans="1:25" ht="78">
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+    </row>
+    <row r="14" spans="1:25" ht="46.5">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="D14" s="1">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>134</v>
+        <v>272</v>
       </c>
       <c r="G14" s="1">
-        <v>32</v>
-      </c>
-      <c r="H14" s="17"/>
-      <c r="I14" s="4" t="s">
-        <v>138</v>
-      </c>
+        <v>610</v>
+      </c>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
       <c r="J14" s="1" t="s">
-        <v>135</v>
+        <v>305</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>137</v>
+        <v>304</v>
       </c>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
@@ -2401,37 +2463,41 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-    </row>
-    <row r="15" spans="1:25" ht="93.6">
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+    </row>
+    <row r="15" spans="1:25" ht="62">
       <c r="A15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B15" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>144</v>
+        <v>277</v>
       </c>
       <c r="D15" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>139</v>
+        <v>2022</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c r="G15" s="1">
-        <v>745</v>
-      </c>
-      <c r="I15" s="17">
-        <v>140933</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>141</v>
+        <v>606</v>
+      </c>
+      <c r="H15" s="17"/>
+      <c r="I15" s="1">
+        <v>127449</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>142</v>
+        <v>278</v>
       </c>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
@@ -2441,38 +2507,40 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-    </row>
-    <row r="16" spans="1:25" ht="62.4">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+    </row>
+    <row r="16" spans="1:25" ht="46.5">
       <c r="A16" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B16" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="D16" s="1">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="G16" s="1">
-        <v>10</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="1">
-        <v>503</v>
+        <v>134</v>
+      </c>
+      <c r="I16" s="17">
+        <v>105093</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>148</v>
+        <v>130</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>131</v>
       </c>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
@@ -2483,36 +2551,37 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
     </row>
-    <row r="17" spans="1:19" ht="62.4">
+    <row r="17" spans="1:19" ht="77.5">
       <c r="A17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="D17" s="1">
         <v>2020</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G17" s="1">
-        <v>126</v>
-      </c>
-      <c r="I17" s="17">
-        <v>104660</v>
+        <v>32</v>
+      </c>
+      <c r="H17" s="17"/>
+      <c r="I17" s="4" t="s">
+        <v>138</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>152</v>
+        <v>135</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>137</v>
       </c>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
@@ -2523,36 +2592,36 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
     </row>
-    <row r="18" spans="1:19" ht="62.4">
+    <row r="18" spans="1:19" ht="93">
       <c r="A18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="D18" s="1">
         <v>2020</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>153</v>
+      <c r="E18" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="G18" s="1">
-        <v>706</v>
+        <v>745</v>
       </c>
       <c r="I18" s="17">
-        <v>135702</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>156</v>
+        <v>140933</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -2563,36 +2632,37 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="1:19" ht="46.8">
+    <row r="19" spans="1:19" ht="62">
       <c r="A19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D19" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="G19" s="1">
-        <v>9</v>
-      </c>
-      <c r="I19" s="17">
-        <v>100260</v>
+        <v>10</v>
+      </c>
+      <c r="H19" s="17"/>
+      <c r="I19" s="1">
+        <v>503</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
@@ -2603,37 +2673,36 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
     </row>
-    <row r="20" spans="1:19" ht="62.4">
+    <row r="20" spans="1:19" ht="62">
       <c r="A20" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B20" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D20" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="G20" s="1">
-        <v>11</v>
-      </c>
-      <c r="H20" s="17">
-        <v>1681</v>
-      </c>
-      <c r="I20" s="1"/>
+        <v>126</v>
+      </c>
+      <c r="I20" s="17">
+        <v>104660</v>
+      </c>
       <c r="J20" s="1" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
@@ -2644,37 +2713,36 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
     </row>
-    <row r="21" spans="1:19" ht="78">
+    <row r="21" spans="1:19" ht="62">
       <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D21" s="1">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H21" s="1"/>
-      <c r="I21" s="4" t="s">
-        <v>173</v>
+        <v>154</v>
+      </c>
+      <c r="G21" s="1">
+        <v>706</v>
+      </c>
+      <c r="I21" s="17">
+        <v>135702</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
@@ -2685,37 +2753,36 @@
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
     </row>
-    <row r="22" spans="1:19" ht="46.8">
+    <row r="22" spans="1:19" ht="46.5">
       <c r="A22" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="D22" s="1">
         <v>2019</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="G22" s="1">
-        <v>111</v>
-      </c>
-      <c r="H22" s="1"/>
-      <c r="I22" s="12" t="s">
-        <v>182</v>
+        <v>9</v>
+      </c>
+      <c r="I22" s="17">
+        <v>100260</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -2726,37 +2793,37 @@
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
     </row>
-    <row r="23" spans="1:19" ht="62.4">
+    <row r="23" spans="1:19" ht="62">
       <c r="A23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="D23" s="1">
         <v>2019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="G23" s="1">
-        <v>64</v>
-      </c>
-      <c r="H23" s="1"/>
-      <c r="I23" s="12" t="s">
-        <v>177</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="H23" s="17">
+        <v>1681</v>
+      </c>
+      <c r="I23" s="1"/>
       <c r="J23" s="1" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -2767,72 +2834,120 @@
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
     </row>
-    <row r="24" spans="1:19" s="16" customFormat="1">
-      <c r="A24" s="13"/>
-      <c r="B24" s="13"/>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="15"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="13"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="13"/>
-    </row>
-    <row r="25" spans="1:19" s="16" customFormat="1">
-      <c r="A25" s="13"/>
-      <c r="B25" s="13"/>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="13"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="13"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="13"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="13"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="13"/>
-      <c r="S25" s="13"/>
-    </row>
-    <row r="26" spans="1:19" ht="78">
+    <row r="24" spans="1:19" ht="77.5">
+      <c r="A24" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="1">
+        <v>22</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+    </row>
+    <row r="25" spans="1:19" ht="46.5">
+      <c r="A25" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="1">
+        <v>23</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2019</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G25" s="1">
+        <v>111</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+    </row>
+    <row r="26" spans="1:19" ht="62">
       <c r="A26" s="1" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="B26" s="1">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>124</v>
+        <v>174</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2019</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="G26" s="1"/>
+        <v>176</v>
+      </c>
+      <c r="G26" s="1">
+        <v>64</v>
+      </c>
       <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+      <c r="I26" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>185</v>
+      </c>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
@@ -2842,260 +2957,246 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
     </row>
-    <row r="27" spans="1:19" s="23" customFormat="1">
-      <c r="A27" s="22"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="22"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="22"/>
-      <c r="S27" s="22"/>
-    </row>
-    <row r="28" spans="1:19" s="25" customFormat="1">
-      <c r="A28" s="24"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
-      <c r="O28" s="24"/>
-      <c r="P28" s="24"/>
-      <c r="Q28" s="24"/>
-      <c r="R28" s="24"/>
-      <c r="S28" s="24"/>
-    </row>
-    <row r="29" spans="1:19" s="27" customFormat="1">
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-    </row>
-    <row r="30" spans="1:19" s="19" customFormat="1">
-      <c r="A30" s="18"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
-      <c r="J30" s="18"/>
-      <c r="K30" s="18"/>
-      <c r="L30" s="18"/>
-      <c r="M30" s="18"/>
-      <c r="N30" s="18"/>
-      <c r="O30" s="18"/>
-      <c r="P30" s="18"/>
-      <c r="Q30" s="18"/>
-      <c r="R30" s="18"/>
-      <c r="S30" s="18"/>
-    </row>
-    <row r="31" spans="1:19" ht="124.8">
-      <c r="A31" s="1" t="s">
+    <row r="27" spans="1:19" s="16" customFormat="1">
+      <c r="A27" s="13"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="13"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="13"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="13"/>
+      <c r="O27" s="13"/>
+      <c r="P27" s="13"/>
+      <c r="Q27" s="13"/>
+      <c r="R27" s="13"/>
+      <c r="S27" s="13"/>
+    </row>
+    <row r="28" spans="1:19" s="16" customFormat="1">
+      <c r="A28" s="13"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="13"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="13"/>
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="13"/>
+      <c r="Q28" s="13"/>
+      <c r="R28" s="13"/>
+      <c r="S28" s="13"/>
+    </row>
+    <row r="29" spans="1:19" ht="62">
+      <c r="A29" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+    </row>
+    <row r="30" spans="1:19" s="23" customFormat="1">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+    </row>
+    <row r="31" spans="1:19" s="25" customFormat="1">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+    </row>
+    <row r="32" spans="1:19" s="27" customFormat="1">
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+    </row>
+    <row r="33" spans="1:19" s="19" customFormat="1">
+      <c r="A33" s="18"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18"/>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="18"/>
+      <c r="R33" s="18"/>
+      <c r="S33" s="18"/>
+    </row>
+    <row r="34" spans="1:19" ht="108.5">
+      <c r="A34" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B34" s="1">
         <v>1</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C34" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D34" s="1">
         <v>2019</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E34" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1" t="s">
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="6" t="s">
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="S31" s="6" t="s">
+      <c r="S34" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="78">
-      <c r="A32" s="1" t="s">
+    <row r="35" spans="1:19" ht="77.5">
+      <c r="A35" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B35" s="1">
         <v>2</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C35" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="D32" s="1">
+      <c r="D35" s="1">
         <v>2019</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E35" s="7" t="s">
         <v>253</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-    </row>
-    <row r="33" spans="1:19" ht="78">
-      <c r="A33" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B33" s="1">
-        <v>3</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D33" s="1">
-        <v>2017</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="S33" s="1"/>
-    </row>
-    <row r="34" spans="1:19" s="19" customFormat="1">
-      <c r="A34" s="18"/>
-      <c r="B34" s="18"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="18"/>
-      <c r="I34" s="18"/>
-      <c r="J34" s="18"/>
-      <c r="K34" s="18"/>
-      <c r="L34" s="18"/>
-      <c r="M34" s="18"/>
-      <c r="N34" s="18"/>
-      <c r="O34" s="18"/>
-      <c r="P34" s="18"/>
-      <c r="Q34" s="18"/>
-      <c r="R34" s="21"/>
-      <c r="S34" s="18"/>
-    </row>
-    <row r="35" spans="1:19" ht="42">
-      <c r="A35" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B35" s="1">
-        <v>1</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="D35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>375</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="K35" s="3" t="s">
+        <v>262</v>
+      </c>
       <c r="L35" s="1"/>
       <c r="M35" s="1" t="s">
-        <v>376</v>
+        <v>259</v>
       </c>
       <c r="N35" s="1"/>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="6"/>
+      <c r="R35" s="1"/>
       <c r="S35" s="1"/>
     </row>
-    <row r="36" spans="1:19" ht="42">
+    <row r="36" spans="1:19" ht="77.5">
       <c r="A36" s="1" t="s">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c r="B36" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>371</v>
+        <v>255</v>
       </c>
       <c r="D36" s="1">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>372</v>
+        <v>254</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -3105,63 +3206,53 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>373</v>
+        <v>259</v>
       </c>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
-      <c r="R36" s="6"/>
+      <c r="R36" s="3" t="s">
+        <v>263</v>
+      </c>
       <c r="S36" s="1"/>
     </row>
-    <row r="37" spans="1:19" ht="42">
-      <c r="A37" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2023</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="1"/>
-    </row>
-    <row r="38" spans="1:19" ht="46.8">
+    <row r="37" spans="1:19" s="19" customFormat="1">
+      <c r="A37" s="18"/>
+      <c r="B37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="18"/>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18"/>
+      <c r="I37" s="18"/>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18"/>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="18"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="18"/>
+    </row>
+    <row r="38" spans="1:19" ht="41.5">
       <c r="A38" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B38" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>322</v>
+        <v>374</v>
       </c>
       <c r="D38" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>323</v>
+        <v>375</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
@@ -3171,30 +3262,30 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1" t="s">
-        <v>324</v>
+        <v>376</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
-      <c r="R38" s="3"/>
+      <c r="R38" s="6"/>
       <c r="S38" s="1"/>
     </row>
-    <row r="39" spans="1:19" ht="46.8">
+    <row r="39" spans="1:19" ht="41.5">
       <c r="A39" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B39" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>322</v>
+        <v>371</v>
       </c>
       <c r="D39" s="1">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>320</v>
+        <v>372</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -3204,30 +3295,30 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1" t="s">
-        <v>321</v>
+        <v>373</v>
       </c>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-      <c r="R39" s="3"/>
+      <c r="R39" s="6"/>
       <c r="S39" s="1"/>
     </row>
-    <row r="40" spans="1:19" ht="42">
+    <row r="40" spans="1:19" ht="41.5">
       <c r="A40" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B40" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>299</v>
+        <v>357</v>
       </c>
       <c r="D40" s="1">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>297</v>
+        <v>358</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -3237,30 +3328,30 @@
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1" t="s">
-        <v>298</v>
+        <v>359</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-      <c r="R40" s="3"/>
+      <c r="R40" s="6"/>
       <c r="S40" s="1"/>
     </row>
-    <row r="41" spans="1:19" ht="42">
+    <row r="41" spans="1:19" ht="46.5">
       <c r="A41" s="1" t="s">
         <v>293</v>
       </c>
       <c r="B41" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>294</v>
+        <v>322</v>
       </c>
       <c r="D41" s="1">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
@@ -3270,7 +3361,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>295</v>
+        <v>324</v>
       </c>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
@@ -3279,12 +3370,22 @@
       <c r="R41" s="3"/>
       <c r="S41" s="1"/>
     </row>
-    <row r="42" spans="1:19">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="7"/>
+    <row r="42" spans="1:19" ht="46.5">
+      <c r="A42" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B42" s="1">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="D42" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>320</v>
+      </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -3292,7 +3393,9 @@
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
+      <c r="M42" s="1" t="s">
+        <v>321</v>
+      </c>
       <c r="N42" s="1"/>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -3300,103 +3403,91 @@
       <c r="R42" s="3"/>
       <c r="S42" s="1"/>
     </row>
-    <row r="43" spans="1:19" s="19" customFormat="1">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-      <c r="K43" s="18"/>
-      <c r="L43" s="18"/>
-      <c r="M43" s="18"/>
-      <c r="N43" s="18"/>
-      <c r="O43" s="18"/>
-      <c r="P43" s="18"/>
-      <c r="Q43" s="18"/>
-      <c r="R43" s="21"/>
-      <c r="S43" s="18"/>
-    </row>
-    <row r="44" spans="1:19" ht="78">
+    <row r="43" spans="1:19" ht="41.5">
+      <c r="A43" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="1">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D43" s="1">
+        <v>2022</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="N43" s="1"/>
+      <c r="O43" s="1"/>
+      <c r="P43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="3"/>
+      <c r="S43" s="1"/>
+    </row>
+    <row r="44" spans="1:19" ht="41.5">
       <c r="A44" s="1" t="s">
-        <v>13</v>
+        <v>293</v>
       </c>
       <c r="B44" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>28</v>
+        <v>294</v>
       </c>
       <c r="D44" s="1">
-        <v>2020</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>14</v>
+        <v>2021</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-      <c r="J44" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>15</v>
-      </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>17</v>
+        <v>295</v>
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
-      <c r="R44" s="1" t="s">
-        <v>82</v>
-      </c>
+      <c r="R44" s="3"/>
       <c r="S44" s="1"/>
     </row>
-    <row r="45" spans="1:19" ht="109.2">
-      <c r="A45" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="1">
-        <v>2</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D45" s="1">
-        <v>2011</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>57</v>
-      </c>
+    <row r="45" spans="1:19">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="7"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
-      <c r="I45" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="I45" s="1"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
-      <c r="L45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
+      <c r="R45" s="3"/>
       <c r="S45" s="1"/>
     </row>
     <row r="46" spans="1:19" s="19" customFormat="1">
@@ -3404,7 +3495,7 @@
       <c r="B46" s="18"/>
       <c r="C46" s="18"/>
       <c r="D46" s="18"/>
-      <c r="E46" s="18"/>
+      <c r="E46" s="20"/>
       <c r="F46" s="18"/>
       <c r="G46" s="18"/>
       <c r="H46" s="18"/>
@@ -3412,125 +3503,118 @@
       <c r="J46" s="18"/>
       <c r="K46" s="18"/>
       <c r="L46" s="18"/>
-      <c r="M46" s="1"/>
+      <c r="M46" s="18"/>
+      <c r="N46" s="18"/>
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
       <c r="Q46" s="18"/>
-      <c r="R46" s="18"/>
+      <c r="R46" s="21"/>
       <c r="S46" s="18"/>
     </row>
-    <row r="47" spans="1:19">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
+    <row r="47" spans="1:19" ht="77.5">
+      <c r="A47" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D47" s="1">
+        <v>2020</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
+      <c r="J47" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
+      <c r="R47" s="1" t="s">
+        <v>82</v>
+      </c>
       <c r="S47" s="1"/>
     </row>
-    <row r="48" spans="1:19" ht="78">
+    <row r="48" spans="1:19" ht="108.5">
       <c r="A48" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B48" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>390</v>
+        <v>29</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2011</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>388</v>
+        <v>57</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="N48" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="O48" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="Q48" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="L48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
     </row>
-    <row r="49" spans="1:23" ht="78">
-      <c r="A49" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B49" s="1">
-        <v>2</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="N49" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O49" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q49" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-    </row>
-    <row r="50" spans="1:23" ht="78">
-      <c r="A50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B50" s="1">
-        <v>3</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>379</v>
-      </c>
+    <row r="49" spans="1:19" s="19" customFormat="1">
+      <c r="A49" s="18"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="18"/>
+      <c r="I49" s="18"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="1"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="18"/>
+      <c r="R49" s="18"/>
+      <c r="S49" s="18"/>
+    </row>
+    <row r="50" spans="1:19">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
       <c r="H50" s="1"/>
@@ -3538,37 +3622,19 @@
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
-      <c r="N50" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="O50" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="Q50" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1"/>
     </row>
-    <row r="51" spans="1:23" ht="109.2">
-      <c r="A51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" s="1">
-        <v>4</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>338</v>
-      </c>
+    <row r="51" spans="1:19">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
@@ -3576,37 +3642,19 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="N51" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O51" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q51" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1"/>
     </row>
-    <row r="52" spans="1:23" ht="109.2">
-      <c r="A52" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="1">
-        <v>5</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>340</v>
-      </c>
+    <row r="52" spans="1:19">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
@@ -3614,36 +3662,28 @@
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="N52" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O52" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q52" s="1" t="b">
-        <v>0</v>
-      </c>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
     </row>
-    <row r="53" spans="1:23" ht="46.8">
+    <row r="53" spans="1:19" ht="77.5">
       <c r="A53" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>334</v>
+        <v>413</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>331</v>
+        <v>417</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>335</v>
+        <v>416</v>
       </c>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
@@ -3653,35 +3693,35 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="N53" s="1" t="s">
-        <v>332</v>
+        <v>410</v>
       </c>
       <c r="O53" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>333</v>
+        <v>411</v>
       </c>
       <c r="Q53" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
     </row>
-    <row r="54" spans="1:23" ht="78">
+    <row r="54" spans="1:19" ht="77.5">
       <c r="A54" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B54" s="1">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>313</v>
+        <v>413</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>311</v>
+        <v>412</v>
       </c>
       <c r="F54" s="1"/>
       <c r="G54" s="1"/>
@@ -3690,37 +3730,36 @@
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
       <c r="N54" s="1" t="s">
-        <v>314</v>
+        <v>414</v>
       </c>
       <c r="O54" s="1" t="b">
         <v>0</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>315</v>
+        <v>415</v>
       </c>
       <c r="Q54" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" s="1"/>
       <c r="S54" s="1"/>
     </row>
-    <row r="55" spans="1:23" ht="109.2">
+    <row r="55" spans="1:19" ht="124">
       <c r="A55" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B55" s="1">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>310</v>
+        <v>407</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>309</v>
+        <v>406</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>306</v>
+        <v>405</v>
       </c>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
@@ -3729,37 +3768,36 @@
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
       <c r="N55" s="1" t="s">
-        <v>307</v>
+        <v>408</v>
       </c>
       <c r="O55" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>308</v>
+        <v>409</v>
       </c>
       <c r="Q55" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="1"/>
       <c r="S55" s="1"/>
     </row>
-    <row r="56" spans="1:23" ht="62.4">
+    <row r="56" spans="1:19" ht="77.5">
       <c r="A56" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B56" s="1">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>283</v>
+        <v>403</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>284</v>
+        <v>402</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>274</v>
+        <v>418</v>
       </c>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
@@ -3768,39 +3806,36 @@
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="O56" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Q56" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q56" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>286</v>
-      </c>
+      <c r="R56" s="1"/>
       <c r="S56" s="1"/>
     </row>
-    <row r="57" spans="1:23" ht="62.4">
+    <row r="57" spans="1:19" ht="77.5">
       <c r="A57" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B57" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>291</v>
+        <v>389</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>284</v>
+        <v>390</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>290</v>
+        <v>388</v>
       </c>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
@@ -3809,39 +3844,36 @@
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
       <c r="N57" s="1" t="s">
-        <v>285</v>
+        <v>391</v>
       </c>
       <c r="O57" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>287</v>
+        <v>392</v>
       </c>
       <c r="Q57" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>292</v>
-      </c>
+      <c r="R57" s="1"/>
       <c r="S57" s="1"/>
     </row>
-    <row r="58" spans="1:23" ht="62.4">
+    <row r="58" spans="1:19" ht="77.5">
       <c r="A58" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B58" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>325</v>
+        <v>387</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>284</v>
+        <v>378</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
@@ -3850,437 +3882,514 @@
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
       <c r="N58" s="1" t="s">
-        <v>285</v>
+        <v>380</v>
       </c>
       <c r="O58" s="1" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>287</v>
+        <v>381</v>
       </c>
       <c r="Q58" s="1" t="b">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>289</v>
-      </c>
+      <c r="R58" s="1"/>
       <c r="S58" s="1"/>
     </row>
-    <row r="59" spans="1:23" ht="93.6">
+    <row r="59" spans="1:19" ht="77.5">
       <c r="A59" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B59" s="1">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>189</v>
+        <v>377</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>378</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="O59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q59" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="W59" s="6" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23" ht="78">
+        <v>379</v>
+      </c>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+      <c r="K59" s="1"/>
+      <c r="L59" s="1"/>
+      <c r="N59" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="O59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q59" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1"/>
+      <c r="S59" s="1"/>
+    </row>
+    <row r="60" spans="1:19" ht="108.5">
       <c r="A60" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B60" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>197</v>
+        <v>341</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="O60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P60" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="Q60" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23" ht="78">
+        <v>338</v>
+      </c>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
+      <c r="K60" s="1"/>
+      <c r="L60" s="1"/>
+      <c r="N60" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="O60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q60" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1"/>
+      <c r="S60" s="1"/>
+    </row>
+    <row r="61" spans="1:19" ht="108.5">
       <c r="A61" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B61" s="1">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>198</v>
+        <v>342</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>337</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O61" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q61" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:23" ht="78">
+        <v>340</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
+      <c r="N61" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="O61" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q61" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1"/>
+      <c r="S61" s="1"/>
+    </row>
+    <row r="62" spans="1:19" ht="46.5">
       <c r="A62" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B62" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>198</v>
+        <v>334</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O62" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q62" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:23" ht="78">
+        <v>335</v>
+      </c>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
+      <c r="K62" s="1"/>
+      <c r="L62" s="1"/>
+      <c r="N62" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="O62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="Q62" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1"/>
+      <c r="S62" s="1"/>
+    </row>
+    <row r="63" spans="1:19" ht="77.5">
       <c r="A63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B63" s="1">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>198</v>
+        <v>313</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O63" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q63" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:23" ht="78">
+        <v>311</v>
+      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O63" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q63" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1"/>
+      <c r="S63" s="1"/>
+    </row>
+    <row r="64" spans="1:19" ht="108.5">
       <c r="A64" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B64" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>198</v>
+        <v>310</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O64" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q64" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19" ht="78">
+        <v>306</v>
+      </c>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
+      <c r="K64" s="1"/>
+      <c r="L64" s="1"/>
+      <c r="M64" s="1"/>
+      <c r="N64" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="O64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="Q64" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1"/>
+      <c r="S64" s="1"/>
+    </row>
+    <row r="65" spans="1:23" ht="62">
       <c r="A65" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B65" s="1">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>198</v>
+        <v>283</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="O65" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="Q65" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19" ht="78">
+        <v>274</v>
+      </c>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q65" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" spans="1:23" ht="62">
       <c r="A66" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B66" s="1">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>211</v>
+        <v>291</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="O66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q66" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R66" s="6" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19" ht="78">
+        <v>290</v>
+      </c>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
+      <c r="K66" s="1"/>
+      <c r="L66" s="1"/>
+      <c r="M66" s="1"/>
+      <c r="N66" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q66" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R66" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" spans="1:23" ht="62">
       <c r="A67" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B67" s="1">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>66</v>
+        <v>325</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="O67" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q67" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19" ht="78">
+        <v>288</v>
+      </c>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q67" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R67" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" spans="1:23" ht="93">
       <c r="A68" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="1">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>219</v>
+        <v>187</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="O68" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="Q68" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="1:19" ht="156">
+      <c r="W68" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="77.5">
       <c r="A69" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B69" s="1">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>221</v>
+        <v>193</v>
       </c>
       <c r="O69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>222</v>
+        <v>194</v>
       </c>
       <c r="Q69" s="2" t="b">
         <v>0</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19" ht="156">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" ht="77.5">
       <c r="A70" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B70" s="1">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>300</v>
+        <v>195</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="O70" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q70" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R70" s="6" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19" ht="156">
+    </row>
+    <row r="71" spans="1:23" ht="77.5">
       <c r="A71" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B71" s="1">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>70</v>
+        <v>198</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>221</v>
+        <v>196</v>
       </c>
       <c r="O71" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="Q71" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="R71" s="6" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" ht="62.4">
+    </row>
+    <row r="72" spans="1:23" ht="77.5">
       <c r="A72" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B72" s="1">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>27</v>
+        <v>198</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="O72" s="2" t="b">
         <v>0</v>
@@ -4292,487 +4401,445 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:19" ht="78">
+    <row r="73" spans="1:23" ht="77.5">
       <c r="A73" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B73" s="1">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>230</v>
+        <v>196</v>
       </c>
       <c r="O73" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="Q73" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:19" ht="46.8">
+    <row r="74" spans="1:23" ht="77.5">
       <c r="A74" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B74" s="1">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>234</v>
+        <v>206</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="O74" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="Q74" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:19" ht="109.2">
+    <row r="75" spans="1:23" ht="62">
       <c r="A75" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B75" s="1">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>249</v>
+        <v>210</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>247</v>
+        <v>212</v>
       </c>
       <c r="O75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>248</v>
+        <v>213</v>
       </c>
       <c r="Q75" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:19" ht="78">
+      <c r="R75" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" ht="77.5">
       <c r="A76" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B76" s="1">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>243</v>
+        <v>66</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="O76" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>241</v>
+        <v>217</v>
       </c>
       <c r="Q76" s="2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:19" ht="78">
+    <row r="77" spans="1:23" ht="77.5">
       <c r="A77" s="1" t="s">
         <v>22</v>
       </c>
       <c r="B77" s="1">
+        <v>25</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q77" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" ht="155">
+      <c r="A78" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B78" s="1">
+        <v>26</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="79" spans="1:23" ht="155">
+      <c r="A79" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B79" s="1">
+        <v>27</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" ht="155">
+      <c r="A80" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80" s="1">
+        <v>28</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" ht="62">
+      <c r="A81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B81" s="1">
+        <v>29</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="Q81" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" ht="77.5">
+      <c r="A82" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82" s="1">
         <v>30</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C82" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="O82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q82" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="46.5">
+      <c r="A83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B83" s="1">
+        <v>31</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="O83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q83" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" ht="108.5">
+      <c r="A84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B84" s="1">
+        <v>32</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="O84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q84" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="77.5">
+      <c r="A85" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85" s="1">
+        <v>33</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="O85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q85" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="77.5">
+      <c r="A86" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B86" s="1">
+        <v>34</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D77" s="2" t="s">
+      <c r="D86" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E86" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="N77" s="2" t="s">
+      <c r="N86" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="O77" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="P77" s="2" t="s">
+      <c r="O86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P86" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Q77" s="2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19" s="19" customFormat="1">
-      <c r="A78" s="18"/>
-      <c r="B78" s="18"/>
-      <c r="C78" s="18"/>
-      <c r="E78" s="18"/>
-    </row>
-    <row r="79" spans="1:19" ht="93.6">
-      <c r="A79" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B79" s="1">
-        <v>1</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D79" s="1">
-        <v>2014</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F79" s="1"/>
-      <c r="G79" s="1"/>
-      <c r="H79" s="1"/>
-      <c r="I79" s="1"/>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="1"/>
-      <c r="M79" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
-      <c r="P79" s="1"/>
-      <c r="Q79" s="1"/>
-      <c r="R79" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="S79" s="1"/>
-    </row>
-    <row r="80" spans="1:19" ht="62.4">
-      <c r="A80" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B80" s="1">
-        <v>2</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="1">
-        <v>2013</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="1"/>
-      <c r="M80" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="N80" s="1"/>
-      <c r="O80" s="1"/>
-      <c r="P80" s="1"/>
-      <c r="Q80" s="1"/>
-      <c r="R80" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S80" s="1"/>
-    </row>
-    <row r="81" spans="1:22" ht="78">
-      <c r="A81" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B81" s="1">
-        <v>3</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D81" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E81" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="1"/>
-      <c r="M81" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N81" s="1"/>
-      <c r="O81" s="1"/>
-      <c r="P81" s="1"/>
-      <c r="Q81" s="1"/>
-      <c r="R81" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="S81" s="1"/>
-    </row>
-    <row r="82" spans="1:22" ht="78">
-      <c r="A82" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B82" s="1">
-        <v>4</v>
-      </c>
-      <c r="C82" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D82" s="1">
-        <v>2012</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="1"/>
-      <c r="M82" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
-      <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
-      <c r="R82" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S82" s="1"/>
-    </row>
-    <row r="83" spans="1:22" ht="109.2">
-      <c r="A83" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B83" s="1">
-        <v>5</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="D83" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E83" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="1"/>
-      <c r="M83" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N83" s="1"/>
-      <c r="O83" s="1"/>
-      <c r="P83" s="1"/>
-      <c r="Q83" s="1"/>
-      <c r="R83" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="S83" s="1"/>
-    </row>
-    <row r="84" spans="1:22" ht="93.6">
-      <c r="A84" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B84" s="1">
-        <v>6</v>
-      </c>
-      <c r="C84" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D84" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E84" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F84" s="1"/>
-      <c r="G84" s="1"/>
-      <c r="H84" s="1"/>
-      <c r="I84" s="1"/>
-      <c r="J84" s="1"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="1"/>
-      <c r="M84" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N84" s="1"/>
-      <c r="O84" s="1"/>
-      <c r="P84" s="1"/>
-      <c r="Q84" s="1"/>
-      <c r="R84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S84" s="1"/>
-    </row>
-    <row r="85" spans="1:22" ht="93.6">
-      <c r="A85" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B85" s="1">
-        <v>7</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D85" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E85" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="F85" s="1"/>
-      <c r="G85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="1"/>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
-      <c r="L85" s="1"/>
-      <c r="M85" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N85" s="1"/>
-      <c r="O85" s="1"/>
-      <c r="P85" s="1"/>
-      <c r="Q85" s="1"/>
-      <c r="R85" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="S85" s="1"/>
-    </row>
-    <row r="86" spans="1:22" ht="93.6">
-      <c r="A86" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B86" s="1">
-        <v>8</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D86" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E86" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F86" s="1"/>
-      <c r="G86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1"/>
-      <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
-      <c r="R86" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="S86" s="1"/>
-    </row>
-    <row r="87" spans="1:22" ht="93.6">
-      <c r="A87" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B87" s="1">
-        <v>9</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D87" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E87" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="1"/>
-      <c r="M87" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="N87" s="1"/>
-      <c r="O87" s="1"/>
-      <c r="P87" s="1"/>
-      <c r="Q87" s="1"/>
-      <c r="R87" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S87" s="1"/>
-    </row>
-    <row r="88" spans="1:22" ht="78">
+      <c r="Q86" s="2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" s="19" customFormat="1">
+      <c r="A87" s="18"/>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="E87" s="18"/>
+    </row>
+    <row r="88" spans="1:19" ht="93">
       <c r="A88" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B88" s="1">
-        <v>10</v>
-      </c>
-      <c r="C88" s="8" t="s">
-        <v>48</v>
+        <v>1</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="D88" s="1">
-        <v>2010</v>
-      </c>
-      <c r="E88" s="8" t="s">
-        <v>64</v>
+        <v>2014</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="F88" s="1"/>
       <c r="G88" s="1"/>
@@ -4781,7 +4848,7 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
-      <c r="M88" s="9" t="s">
+      <c r="M88" s="1" t="s">
         <v>38</v>
       </c>
       <c r="N88" s="1"/>
@@ -4789,415 +4856,733 @@
       <c r="P88" s="1"/>
       <c r="Q88" s="1"/>
       <c r="R88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="S88" s="1"/>
+    </row>
+    <row r="89" spans="1:19" ht="62">
+      <c r="A89" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B89" s="1">
+        <v>2</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="1">
+        <v>2013</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" s="1"/>
+      <c r="G89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="I89" s="1"/>
+      <c r="J89" s="1"/>
+      <c r="K89" s="1"/>
+      <c r="L89" s="1"/>
+      <c r="M89" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="S89" s="1"/>
+    </row>
+    <row r="90" spans="1:19" ht="77.5">
+      <c r="A90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B90" s="1">
+        <v>3</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D90" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E90" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F90" s="1"/>
+      <c r="G90" s="1"/>
+      <c r="H90" s="1"/>
+      <c r="I90" s="1"/>
+      <c r="J90" s="1"/>
+      <c r="K90" s="1"/>
+      <c r="L90" s="1"/>
+      <c r="M90" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N90" s="1"/>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="S90" s="1"/>
+    </row>
+    <row r="91" spans="1:19" ht="77.5">
+      <c r="A91" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B91" s="1">
+        <v>4</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D91" s="1">
+        <v>2012</v>
+      </c>
+      <c r="E91" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F91" s="1"/>
+      <c r="G91" s="1"/>
+      <c r="H91" s="1"/>
+      <c r="I91" s="1"/>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="1"/>
+      <c r="M91" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N91" s="1"/>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="S91" s="1"/>
+    </row>
+    <row r="92" spans="1:19" ht="108.5">
+      <c r="A92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92" s="1">
+        <v>5</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E92" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F92" s="1"/>
+      <c r="G92" s="1"/>
+      <c r="H92" s="1"/>
+      <c r="I92" s="1"/>
+      <c r="J92" s="1"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="1"/>
+      <c r="M92" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N92" s="1"/>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S92" s="1"/>
+    </row>
+    <row r="93" spans="1:19" ht="93">
+      <c r="A93" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" s="1">
+        <v>6</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="F93" s="1"/>
+      <c r="G93" s="1"/>
+      <c r="H93" s="1"/>
+      <c r="I93" s="1"/>
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N93" s="1"/>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S93" s="1"/>
+    </row>
+    <row r="94" spans="1:19" ht="93">
+      <c r="A94" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B94" s="1">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E94" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" s="1"/>
+      <c r="G94" s="1"/>
+      <c r="H94" s="1"/>
+      <c r="I94" s="1"/>
+      <c r="J94" s="1"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="1"/>
+      <c r="M94" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N94" s="1"/>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S94" s="1"/>
+    </row>
+    <row r="95" spans="1:19" ht="93">
+      <c r="A95" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B95" s="1">
+        <v>8</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D95" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E95" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F95" s="1"/>
+      <c r="G95" s="1"/>
+      <c r="H95" s="1"/>
+      <c r="I95" s="1"/>
+      <c r="J95" s="1"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="1"/>
+      <c r="M95" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="S95" s="1"/>
+    </row>
+    <row r="96" spans="1:19" ht="93">
+      <c r="A96" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B96" s="1">
+        <v>9</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D96" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E96" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F96" s="1"/>
+      <c r="G96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="1"/>
+      <c r="M96" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="R96" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="S96" s="1"/>
+    </row>
+    <row r="97" spans="1:22" ht="77.5">
+      <c r="A97" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B97" s="1">
+        <v>10</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2010</v>
+      </c>
+      <c r="E97" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F97" s="1"/>
+      <c r="G97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="1"/>
+      <c r="M97" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="S88" s="1"/>
-    </row>
-    <row r="89" spans="1:22" ht="234">
-      <c r="A89" s="1" t="s">
+      <c r="S97" s="1"/>
+    </row>
+    <row r="98" spans="1:22" ht="232.5">
+      <c r="A98" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B89" s="1">
+      <c r="B98" s="1">
         <v>1</v>
-      </c>
-      <c r="C89" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E89" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="P89" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q89" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T89" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" ht="62.4">
-      <c r="A90" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B90" s="1">
-        <v>2</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N90" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P90" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q90" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T90" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" ht="62.4">
-      <c r="A91" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91" s="1">
-        <v>3</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="N91" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P91" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q91" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T91" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" ht="78">
-      <c r="A92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B92" s="1">
-        <v>4</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="N92" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="P92" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q92" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T92" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" ht="78">
-      <c r="A93" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B93" s="1">
-        <v>1</v>
-      </c>
-      <c r="C93" s="10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D93" s="2">
-        <v>2020</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="S93" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="U93" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="V93" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" ht="62.4">
-      <c r="A94" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B94" s="1">
-        <v>2</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="D94" s="2">
-        <v>2019</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="S94" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="U94" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" ht="62.4">
-      <c r="A95" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B95" s="1">
-        <v>3</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="S95" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U95" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" ht="78">
-      <c r="A96" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B96" s="1">
-        <v>4</v>
-      </c>
-      <c r="C96" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E96" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="U96" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="V96" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="97" spans="1:22" ht="62.4">
-      <c r="A97" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B97" s="1">
-        <v>5</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2">
-        <v>2016</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="U97" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="98" spans="1:22" ht="62.4">
-      <c r="A98" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B98" s="1">
-        <v>6</v>
       </c>
       <c r="C98" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D98" s="2">
-        <v>2015</v>
+      <c r="D98" s="2" t="s">
+        <v>66</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="U98" s="10" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="99" spans="1:22" ht="93.6">
+        <v>67</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" ht="62">
       <c r="A99" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="B99" s="1">
+        <v>2</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q99" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="D99" s="2">
-        <v>2018</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R99" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="U99" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" ht="78">
+      <c r="T99" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" ht="62">
       <c r="A100" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="B100" s="1">
-        <v>2</v>
-      </c>
-      <c r="C100" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="D100" s="2">
-        <v>2018</v>
+        <v>3</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="R100" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="U100" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="V100" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" ht="93.6">
+        <v>76</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="P100" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q100" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T100" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" ht="77.5">
       <c r="A101" s="1" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="B101" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C101" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D101" s="2">
+      <c r="D101" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q101" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" ht="77.5">
+      <c r="A102" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="1">
+        <v>1</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D102" s="2">
+        <v>2020</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="U102" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" ht="62">
+      <c r="A103" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" s="1">
+        <v>2</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="D103" s="2">
         <v>2019</v>
       </c>
-      <c r="E101" s="10" t="s">
+      <c r="E103" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="S103" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22" ht="46.5">
+      <c r="A104" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B104" s="1">
+        <v>3</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="S104" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="U104" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" ht="77.5">
+      <c r="A105" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="1">
+        <v>4</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="V105" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" ht="46.5">
+      <c r="A106" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="1">
+        <v>5</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="2">
+        <v>2016</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="U106" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" ht="62">
+      <c r="A107" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B107" s="1">
+        <v>6</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="2">
+        <v>2015</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="S107" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="U107" s="10" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22" ht="93">
+      <c r="A108" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B108" s="1">
+        <v>1</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="D108" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="U108" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22" ht="77.5">
+      <c r="A109" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B109" s="1">
+        <v>2</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" s="2">
+        <v>2018</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="S109" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="U109" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22" ht="93">
+      <c r="A110" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B110" s="1">
+        <v>1</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D110" s="2">
+        <v>2019</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="R101" s="2" t="s">
+      <c r="R110" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S101" s="2" t="s">
+      <c r="S110" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="102" spans="1:22" ht="46.8">
-      <c r="A102" s="1" t="s">
+    <row r="111" spans="1:22" ht="46.5">
+      <c r="A111" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B102" s="1">
+      <c r="B111" s="1">
         <v>2</v>
       </c>
-      <c r="C102" s="8" t="s">
+      <c r="C111" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D102" s="2">
+      <c r="D111" s="2">
         <v>2019</v>
       </c>
-      <c r="E102" s="11" t="s">
+      <c r="E111" s="11" t="s">
         <v>114</v>
       </c>
-      <c r="R102" s="2" t="s">
+      <c r="R111" s="2" t="s">
         <v>115</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B15:K25">
-    <sortCondition ref="B15:B25"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B18:K28">
+    <sortCondition ref="B18:B28"/>
   </sortState>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="J44" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
-    <hyperlink ref="K13" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
-    <hyperlink ref="K14" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
-    <hyperlink ref="K15" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
-    <hyperlink ref="K16" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
-    <hyperlink ref="K17" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
-    <hyperlink ref="K18" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
-    <hyperlink ref="K19" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
-    <hyperlink ref="K20" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
-    <hyperlink ref="K21" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
-    <hyperlink ref="K23" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
-    <hyperlink ref="K22" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
-    <hyperlink ref="R31" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
-    <hyperlink ref="S31" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
-    <hyperlink ref="K32" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
-    <hyperlink ref="R33" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
-    <hyperlink ref="W59" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
-    <hyperlink ref="R71" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
-    <hyperlink ref="R70" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
-    <hyperlink ref="R69" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
-    <hyperlink ref="R66" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
-    <hyperlink ref="R60" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
-    <hyperlink ref="K12" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
-    <hyperlink ref="J12" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
-    <hyperlink ref="R56" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
-    <hyperlink ref="R58" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
-    <hyperlink ref="R57" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
-    <hyperlink ref="K11" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
-    <hyperlink ref="K10" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
-    <hyperlink ref="K8" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
-    <hyperlink ref="K9" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
-    <hyperlink ref="K7" r:id="rId32" xr:uid="{824F3703-A805-4B51-BA57-B640C8BF73D3}"/>
-    <hyperlink ref="K5" r:id="rId33" xr:uid="{E5CFF721-38D6-4448-93C3-951FBBF29F8D}"/>
-    <hyperlink ref="K6" r:id="rId34" xr:uid="{E1B605ED-C040-417B-B4C4-B1FC7C626113}"/>
-    <hyperlink ref="K3" r:id="rId35" xr:uid="{010600D1-2BBC-ED47-B823-FD451BF3D204}"/>
-    <hyperlink ref="K2" r:id="rId36" xr:uid="{00771DC6-BDA8-E948-8810-7573A19F1264}"/>
+    <hyperlink ref="J47" r:id="rId1" display="https://doi.org/10.4324/9780429260919" xr:uid="{1DDAA8A2-3DE9-D743-A79F-D2981E5790DA}"/>
+    <hyperlink ref="K16" r:id="rId2" xr:uid="{BA548D61-5286-450E-B5D8-9CA662E78DF1}"/>
+    <hyperlink ref="K17" r:id="rId3" xr:uid="{7D4967E5-40CC-4954-8327-6A772AA2A957}"/>
+    <hyperlink ref="K18" r:id="rId4" xr:uid="{12F12244-BD30-4FBD-A236-09F2ECD3778F}"/>
+    <hyperlink ref="K19" r:id="rId5" xr:uid="{0BEA2CC2-508D-4C8C-AA81-4F63390D1A26}"/>
+    <hyperlink ref="K20" r:id="rId6" xr:uid="{8B83B70B-0708-4C66-82E7-DCE04D32C18D}"/>
+    <hyperlink ref="K21" r:id="rId7" xr:uid="{7882D75E-15F6-4B33-B047-F71E5823344F}"/>
+    <hyperlink ref="K22" r:id="rId8" xr:uid="{F940BC28-68A7-4220-9F3C-2CE3B1862ABB}"/>
+    <hyperlink ref="K23" r:id="rId9" xr:uid="{1DA1A95D-7850-4DFF-B869-CDDB7D086AE6}"/>
+    <hyperlink ref="K24" r:id="rId10" xr:uid="{5D3260F5-3897-4531-BC12-BB45E34B149A}"/>
+    <hyperlink ref="K26" r:id="rId11" xr:uid="{DAC6D232-E160-403D-AA2A-0066D71FD892}"/>
+    <hyperlink ref="K25" r:id="rId12" xr:uid="{7A6F013C-478F-4A54-B4B9-C9B5D6702479}"/>
+    <hyperlink ref="R34" r:id="rId13" xr:uid="{2D7B0E01-5671-4FB6-9267-9700EF4AACF9}"/>
+    <hyperlink ref="S34" r:id="rId14" xr:uid="{DB40CF40-6052-4684-B7F4-3903CF78FA52}"/>
+    <hyperlink ref="K35" r:id="rId15" xr:uid="{B4F8683C-58D8-49FD-BB54-98C67A4D0B8C}"/>
+    <hyperlink ref="R36" r:id="rId16" xr:uid="{37F06173-A112-43F7-92B2-74C697F2B8BC}"/>
+    <hyperlink ref="W68" r:id="rId17" xr:uid="{1B126FCA-8446-4E08-8C87-760F2A8F12CC}"/>
+    <hyperlink ref="R80" r:id="rId18" xr:uid="{ED9D7A6D-68ED-445E-ABD4-2AAC6A999A6E}"/>
+    <hyperlink ref="R79" r:id="rId19" xr:uid="{27B729C7-E9EA-4A89-873C-907E005DD138}"/>
+    <hyperlink ref="R78" r:id="rId20" xr:uid="{8581B660-5FBA-471F-A8F1-069DB8EB782D}"/>
+    <hyperlink ref="R75" r:id="rId21" xr:uid="{5F0EB864-8594-40CD-A4CE-D2F32BC318DF}"/>
+    <hyperlink ref="R69" r:id="rId22" xr:uid="{F74DCF66-DE4A-4CD6-9326-62F58C8D0088}"/>
+    <hyperlink ref="K15" r:id="rId23" xr:uid="{A49517BD-EE25-403D-8EAA-84E43D781FEB}"/>
+    <hyperlink ref="J15" r:id="rId24" display="https://doi.org/10.1016/j.jhydrol.2022.127449" xr:uid="{8D3E252A-DBD2-45D2-897D-6F2D25B0714D}"/>
+    <hyperlink ref="R65" r:id="rId25" xr:uid="{C2C2BED0-6A13-4819-91BC-2F9C49F5489B}"/>
+    <hyperlink ref="R67" r:id="rId26" xr:uid="{B29AA9BF-EE4A-45A5-B36A-E4ACCB6B75EE}"/>
+    <hyperlink ref="R66" r:id="rId27" xr:uid="{9710E869-58A6-4F5F-A7E8-57CE38A208D7}"/>
+    <hyperlink ref="K14" r:id="rId28" xr:uid="{B79FF0E4-1AE9-46AE-8E9A-0F2A844277F7}"/>
+    <hyperlink ref="K13" r:id="rId29" xr:uid="{2CFBDD80-2C8E-4C0C-BF45-FF5B99D9AF51}"/>
+    <hyperlink ref="K11" r:id="rId30" xr:uid="{2A765B15-3B0B-4BAF-95AD-4FC851D8343D}"/>
+    <hyperlink ref="K12" r:id="rId31" xr:uid="{7D61F22C-7D64-491C-BA97-44A28B404208}"/>
+    <hyperlink ref="K10" r:id="rId32" xr:uid="{824F3703-A805-4B51-BA57-B640C8BF73D3}"/>
+    <hyperlink ref="K8" r:id="rId33" xr:uid="{E5CFF721-38D6-4448-93C3-951FBBF29F8D}"/>
+    <hyperlink ref="K9" r:id="rId34" xr:uid="{E1B605ED-C040-417B-B4C4-B1FC7C626113}"/>
+    <hyperlink ref="K6" r:id="rId35" xr:uid="{010600D1-2BBC-ED47-B823-FD451BF3D204}"/>
+    <hyperlink ref="K5" r:id="rId36" xr:uid="{00771DC6-BDA8-E948-8810-7573A19F1264}"/>
+    <hyperlink ref="J3" r:id="rId37" display="https://doi.org/10.1016/j.agwat.2026.110313" xr:uid="{3B334DD8-E6C0-468E-A715-F3EECC9E96B3}"/>
+    <hyperlink ref="K3" r:id="rId38" xr:uid="{3FF71B43-CFE7-4CB3-B3B5-3CBD1A17B104}"/>
+    <hyperlink ref="K4" r:id="rId39" xr:uid="{7A31FA31-5793-44F3-8243-F0DBCE5C8023}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId40"/>
 </worksheet>
 </file>